--- a/exports/COCHINSHIP_full_report.xlsx
+++ b/exports/COCHINSHIP_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.25</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>172.4</v>
+        <v>167.75</v>
       </c>
       <c r="I2" t="n">
         <v>169.99426248</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.32</v>
+        <v>-3.98</v>
       </c>
       <c r="L2" t="n">
-        <v>1.55</v>
+        <v>4.44</v>
       </c>
       <c r="M2" t="n">
         <v>0.11</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2.84</v>
       </c>
       <c r="O2" t="n">
         <v>0.2</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.67</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44630.55208333334</v>
+        <v>44631.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>148.5</v>
+        <v>152.05</v>
       </c>
       <c r="I3" t="n">
         <v>149.485844486982</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K3" t="n">
-        <v>11.48</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>3.73</v>
@@ -612,7 +647,7 @@
         <v>2.84</v>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
         <v>-2.84</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>6.99</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>163.5</v>
+        <v>159</v>
       </c>
       <c r="I4" t="n">
         <v>161.9433210936265</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K4" t="n">
-        <v>7.53</v>
+        <v>4.57</v>
       </c>
       <c r="L4" t="n">
         <v>4.54</v>
       </c>
       <c r="M4" t="n">
-        <v>0.89</v>
+        <v>1.53</v>
       </c>
       <c r="N4" t="n">
         <v>5.09</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44698.38541666666</v>
+        <v>44698.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>160.6</v>
+        <v>164.3</v>
       </c>
       <c r="I5" t="n">
         <v>162.7596611367775</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.01</v>
+        <v>-3.33</v>
       </c>
       <c r="L5" t="n">
-        <v>2.26</v>
+        <v>3.71</v>
       </c>
       <c r="M5" t="n">
         <v>1.47</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>158</v>
+        <v>154.15</v>
       </c>
       <c r="I6" t="n">
         <v>157.5351901127259</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.83</v>
+        <v>-6.18</v>
       </c>
       <c r="L6" t="n">
-        <v>5.36</v>
+        <v>6.27</v>
       </c>
       <c r="M6" t="n">
         <v>2.65</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.75</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44749.55208333334</v>
+        <v>44750.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>158.5</v>
+        <v>159.1</v>
       </c>
       <c r="I7" t="n">
         <v>158.7655762626646</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.82</v>
+        <v>-3.21</v>
       </c>
       <c r="L7" t="n">
-        <v>3.47</v>
+        <v>3.67</v>
       </c>
       <c r="M7" t="n">
         <v>1.29</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>3.75</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>315.5</v>
+        <v>309</v>
       </c>
       <c r="I8" t="n">
         <v>310.5553324427073</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>153.1666666666667</v>
+        <v>154</v>
       </c>
       <c r="K8" t="n">
-        <v>98.3</v>
+        <v>94.22</v>
       </c>
       <c r="L8" t="n">
         <v>1.13</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>207</v>
+        <v>208</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.7</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45002.55208333334</v>
+        <v>45005.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>222</v>
+        <v>231.95</v>
       </c>
       <c r="I9" t="n">
         <v>231.9263129909881</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>98.16666666666667</v>
+        <v>101</v>
       </c>
       <c r="K9" t="n">
-        <v>28.16</v>
+        <v>24.94</v>
       </c>
       <c r="L9" t="n">
         <v>4.66</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>8.08</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45009.55208333334</v>
+        <v>45012.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>216.7</v>
+        <v>211.2</v>
       </c>
       <c r="I10" t="n">
         <v>213.2181210466127</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.57</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>7.31</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>-0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.69</v>
+        <v>4.71</v>
       </c>
       <c r="O10" t="n">
         <v>3.42</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45014.38541666666</v>
+        <v>45014.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>212.6</v>
+        <v>233</v>
       </c>
       <c r="I11" t="n">
         <v>224.1096847335377</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.66</v>
+        <v>-10.32</v>
       </c>
       <c r="L11" t="n">
-        <v>2.98</v>
+        <v>12.22</v>
       </c>
       <c r="M11" t="n">
         <v>0.48</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>12.77</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45065.55208333334</v>
+        <v>45068.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>271.9</v>
+        <v>244.65</v>
       </c>
       <c r="I12" t="n">
         <v>260.90087662049</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>16.7</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
         <v>8.84</v>
       </c>
       <c r="M12" t="n">
-        <v>0.41</v>
+        <v>10.63</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>10.46</v>
       </c>
       <c r="O12" t="n">
         <v>11.51</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45079.55208333334</v>
+        <v>45082.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>250.5</v>
+        <v>273.4</v>
       </c>
       <c r="I13" t="n">
         <v>254.702934106985</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.39</v>
+        <v>-11.75</v>
       </c>
       <c r="L13" t="n">
-        <v>3.78</v>
+        <v>11.81</v>
       </c>
       <c r="M13" t="n">
         <v>0.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>11.42</v>
       </c>
       <c r="O13" t="n">
         <v>-10.46</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.15</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>548.7</v>
+        <v>536.5</v>
       </c>
       <c r="I14" t="n">
         <v>540.2652620669498</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>99</v>
+        <v>99.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>100.69</v>
+        <v>96.23</v>
       </c>
       <c r="L14" t="n">
         <v>9.07</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>17.28</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45195.55208333334</v>
+        <v>45196.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>542.85</v>
+        <v>550.95</v>
       </c>
       <c r="I15" t="n">
         <v>550.5665514454978</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.18</v>
+        <v>-2.69</v>
       </c>
       <c r="L15" t="n">
         <v>6.24</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>12.56</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>503.4</v>
+        <v>485.5</v>
       </c>
       <c r="I16" t="n">
         <v>486.0682923108886</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.630000000000001</v>
+        <v>-11.88</v>
       </c>
       <c r="L16" t="n">
-        <v>9.25</v>
+        <v>11.97</v>
       </c>
       <c r="M16" t="n">
         <v>2.79</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.95</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45236.38541666666</v>
+        <v>45236.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>492.25</v>
+        <v>504</v>
       </c>
       <c r="I17" t="n">
         <v>499.5875099699135</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.39</v>
+        <v>-3.81</v>
       </c>
       <c r="L17" t="n">
         <v>7.05</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>883.25</v>
+        <v>824.5</v>
       </c>
       <c r="I18" t="n">
         <v>838.1941200767359</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>95</v>
+        <v>97.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>75.25</v>
+        <v>63.59</v>
       </c>
       <c r="L18" t="n">
         <v>2.44</v>
@@ -1467,7 +1682,7 @@
         <v>1.59</v>
       </c>
       <c r="N18" t="n">
-        <v>6.34</v>
+        <v>7.6</v>
       </c>
       <c r="O18" t="n">
         <v>6.89</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>13.84</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45365.55208333334</v>
+        <v>45366.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>808.25</v>
+        <v>853.65</v>
       </c>
       <c r="I19" t="n">
         <v>829.1693172566429</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K19" t="n">
-        <v>1.97</v>
+        <v>-3.54</v>
       </c>
       <c r="L19" t="n">
         <v>10.83</v>
@@ -1524,7 +1751,7 @@
         <v>1.52</v>
       </c>
       <c r="N19" t="n">
-        <v>9.220000000000001</v>
+        <v>10.98</v>
       </c>
       <c r="O19" t="n">
         <v>-7.6</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>16.93</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45422.55208333334</v>
+        <v>45425.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1236.8</v>
+        <v>1180.05</v>
       </c>
       <c r="I20" t="n">
         <v>1200.558351186063</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K20" t="n">
-        <v>44.88</v>
+        <v>38.24</v>
       </c>
       <c r="L20" t="n">
         <v>7.62</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>14.03</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45426.38541666666</v>
+        <v>45426.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>1303.8</v>
+        <v>1335</v>
       </c>
       <c r="I21" t="n">
         <v>1326.126066364981</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.49</v>
+        <v>-13.13</v>
       </c>
       <c r="L21" t="n">
-        <v>11.01</v>
+        <v>14.83</v>
       </c>
       <c r="M21" t="n">
         <v>4.01</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>12.34</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45447.55208333334</v>
+        <v>45448.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1811.7</v>
+        <v>1691.8</v>
       </c>
       <c r="I22" t="n">
         <v>1749.560194576655</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>35.71</v>
+        <v>26.73</v>
       </c>
       <c r="L22" t="n">
         <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>0.52</v>
+        <v>1.2</v>
       </c>
       <c r="N22" t="n">
         <v>9.91</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>19.89</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45456.38541666666</v>
+        <v>45456.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>1921</v>
+        <v>2010.1</v>
       </c>
       <c r="I23" t="n">
         <v>2008.562640954431</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>-13.55</v>
+        <v>-18.81</v>
       </c>
       <c r="L23" t="n">
-        <v>15.5</v>
+        <v>19.28</v>
       </c>
       <c r="M23" t="n">
         <v>2.67</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>12.39</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>2625</v>
+        <v>2547.25</v>
       </c>
       <c r="I24" t="n">
         <v>2547.688300481787</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K24" t="n">
-        <v>30.59</v>
+        <v>26.72</v>
       </c>
       <c r="L24" t="n">
         <v>5.13</v>
       </c>
       <c r="M24" t="n">
-        <v>0.18</v>
+        <v>0.57</v>
       </c>
       <c r="N24" t="n">
         <v>4.37</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>14.01</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45554.55208333334</v>
+        <v>45555.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1688</v>
+        <v>1846.05</v>
       </c>
       <c r="I25" t="n">
         <v>1812.99613014581</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K25" t="n">
-        <v>33.73</v>
+        <v>27.53</v>
       </c>
       <c r="L25" t="n">
         <v>8.92</v>
@@ -1866,7 +2165,7 @@
         <v>5.73</v>
       </c>
       <c r="N25" t="n">
-        <v>4.72</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-2.86</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>14</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45561.55208333334</v>
+        <v>45562.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1709.95</v>
+        <v>1680.1</v>
       </c>
       <c r="I26" t="n">
         <v>1695.938121123705</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.37</v>
+        <v>-8.99</v>
       </c>
       <c r="L26" t="n">
         <v>9.970000000000001</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>11.64</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45595.55208333334</v>
+        <v>45596.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1472.1</v>
+        <v>1495</v>
       </c>
       <c r="I27" t="n">
         <v>1489.343734769204</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K27" t="n">
-        <v>12.38</v>
+        <v>11.02</v>
       </c>
       <c r="L27" t="n">
         <v>6.06</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.17</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45607.38541666666</v>
+        <v>45607.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>1407</v>
+        <v>1399.95</v>
       </c>
       <c r="I28" t="n">
         <v>1405.960078585971</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.89</v>
+        <v>-6.36</v>
       </c>
       <c r="L28" t="n">
         <v>7.79</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>8.75</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45621.55208333334</v>
+        <v>45622.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1364.25</v>
+        <v>1432.45</v>
       </c>
       <c r="I29" t="n">
         <v>1399.284696653753</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>2.55</v>
+        <v>-2.32</v>
       </c>
       <c r="L29" t="n">
-        <v>1.18</v>
+        <v>2.32</v>
       </c>
       <c r="M29" t="n">
         <v>4.46</v>
       </c>
       <c r="N29" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
         <v>-3.29</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1618</v>
+        <v>1565</v>
       </c>
       <c r="I30" t="n">
         <v>1570.326922500768</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K30" t="n">
-        <v>12.95</v>
+        <v>9.25</v>
       </c>
       <c r="L30" t="n">
         <v>4.01</v>
@@ -2151,7 +2510,7 @@
         <v>0.31</v>
       </c>
       <c r="N30" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1568</v>
+        <v>1594.4</v>
       </c>
       <c r="I31" t="n">
         <v>1590.209804141811</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.19</v>
+        <v>-1.88</v>
       </c>
       <c r="L31" t="n">
         <v>3.81</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>10.68</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="I32" t="n">
         <v>1458.698733335247</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K32" t="n">
-        <v>-7.8</v>
+        <v>-8.93</v>
       </c>
       <c r="L32" t="n">
-        <v>8.33</v>
+        <v>11.25</v>
       </c>
       <c r="M32" t="n">
         <v>0.95</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.67</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45673.55208333334</v>
+        <v>45674.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1449.95</v>
+        <v>1502.65</v>
       </c>
       <c r="I33" t="n">
         <v>1486.700672415664</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>0.14</v>
+        <v>-3.49</v>
       </c>
       <c r="L33" t="n">
-        <v>1.93</v>
+        <v>4.27</v>
       </c>
       <c r="M33" t="n">
         <v>1.98</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>10.05</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1456</v>
+        <v>1414.85</v>
       </c>
       <c r="I34" t="n">
         <v>1428.280829739542</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.1</v>
+        <v>-5.84</v>
       </c>
       <c r="L34" t="n">
-        <v>4.17</v>
+        <v>7.5</v>
       </c>
       <c r="M34" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="N34" t="n">
-        <v>2.85</v>
+        <v>3.64</v>
       </c>
       <c r="O34" t="n">
         <v>3.24</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45688.38541666666</v>
+        <v>45688.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1516.4</v>
+        <v>1537</v>
       </c>
       <c r="I35" t="n">
         <v>1526.5905165984</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.18</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>8.140000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="M35" t="n">
         <v>0.93</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>9.5</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45694.55208333334</v>
+        <v>45695.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1408</v>
+        <v>1360.35</v>
       </c>
       <c r="I36" t="n">
         <v>1390.941100466587</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>-8.390000000000001</v>
+        <v>-11.49</v>
       </c>
       <c r="L36" t="n">
-        <v>9.56</v>
+        <v>13.14</v>
       </c>
       <c r="M36" t="n">
-        <v>0.82</v>
+        <v>5.18</v>
       </c>
       <c r="N36" t="n">
         <v>4.88</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>9.23</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1343</v>
+        <v>1441.85</v>
       </c>
       <c r="I37" t="n">
         <v>1349.443252413748</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K37" t="n">
-        <v>1.28</v>
+        <v>-5.99</v>
       </c>
       <c r="L37" t="n">
-        <v>5.12</v>
+        <v>6.91</v>
       </c>
       <c r="M37" t="n">
         <v>1.54</v>
       </c>
       <c r="N37" t="n">
-        <v>4.61</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O37" t="n">
         <v>-3.27</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>11.15</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1392.3</v>
+        <v>1316.6</v>
       </c>
       <c r="I38" t="n">
         <v>1361.253273275298</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.44</v>
+        <v>-8.69</v>
       </c>
       <c r="L38" t="n">
-        <v>6.9</v>
+        <v>15.07</v>
       </c>
       <c r="M38" t="n">
-        <v>0.82</v>
+        <v>11.3</v>
       </c>
       <c r="N38" t="n">
         <v>4.96</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>9.58</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1403</v>
+        <v>1451.1</v>
       </c>
       <c r="I39" t="n">
         <v>1442.728636354872</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.56</v>
+        <v>-10.22</v>
       </c>
       <c r="L39" t="n">
-        <v>9.470000000000001</v>
+        <v>12.71</v>
       </c>
       <c r="M39" t="n">
         <v>3.34</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>10.49</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45783.55208333334</v>
+        <v>45784.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1478</v>
+        <v>1462.5</v>
       </c>
       <c r="I40" t="n">
         <v>1477.745274014479</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K40" t="n">
-        <v>1.85</v>
+        <v>0.79</v>
       </c>
       <c r="L40" t="n">
         <v>3.3</v>
       </c>
       <c r="M40" t="n">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="N40" t="n">
         <v>4.27</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>13.79</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45790.55208333334</v>
+        <v>45791.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1577</v>
+        <v>1759.2</v>
       </c>
       <c r="I41" t="n">
         <v>1608.713510811293</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.83</v>
+        <v>-20.29</v>
       </c>
       <c r="L41" t="n">
-        <v>8.890000000000001</v>
+        <v>22.94</v>
       </c>
       <c r="M41" t="n">
-        <v>2.75</v>
+        <v>3.99</v>
       </c>
       <c r="N41" t="n">
-        <v>3.68</v>
+        <v>7.79</v>
       </c>
       <c r="O41" t="n">
         <v>-0.98</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>13.14</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45819.55208333334</v>
+        <v>45820.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2193.2</v>
+        <v>2175.9</v>
       </c>
       <c r="I42" t="n">
         <v>2181.477604813592</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K42" t="n">
-        <v>24.67</v>
+        <v>23.69</v>
       </c>
       <c r="L42" t="n">
         <v>6.78</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.5</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45901.55208333334</v>
+        <v>45902.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1680</v>
+        <v>1748.5</v>
       </c>
       <c r="I43" t="n">
         <v>1696.633835675787</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>81.16666666666667</v>
+        <v>82</v>
       </c>
       <c r="K43" t="n">
-        <v>22.79</v>
+        <v>19.64</v>
       </c>
       <c r="L43" t="n">
         <v>4.69</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>8.85</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45908.55208333334</v>
+        <v>45909.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1650</v>
+        <v>1633.4</v>
       </c>
       <c r="I44" t="n">
         <v>1634.966032876162</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.63</v>
+        <v>-6.58</v>
       </c>
       <c r="L44" t="n">
-        <v>5.91</v>
+        <v>6.78</v>
       </c>
       <c r="M44" t="n">
         <v>-0</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>7.18</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45912.38541666666</v>
+        <v>45912.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>1725.6</v>
+        <v>1753.9</v>
       </c>
       <c r="I45" t="n">
         <v>1728.425036672978</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.64</v>
+        <v>-7.38</v>
       </c>
       <c r="L45" t="n">
-        <v>6.45</v>
+        <v>7.44</v>
       </c>
       <c r="M45" t="n">
         <v>0.41</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45926.55208333334</v>
+        <v>45929.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1880</v>
+        <v>1801.3</v>
       </c>
       <c r="I46" t="n">
         <v>1814.413890910177</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>7.19</v>
+        <v>2.7</v>
       </c>
       <c r="L46" t="n">
         <v>2.69</v>
@@ -3063,7 +3614,7 @@
         <v>0.01</v>
       </c>
       <c r="N46" t="n">
-        <v>2.64</v>
+        <v>5.32</v>
       </c>
       <c r="O46" t="n">
         <v>6.39</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.62</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1762</v>
+        <v>1791.2</v>
       </c>
       <c r="I47" t="n">
         <v>1772.099280091746</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K47" t="n">
-        <v>2.18</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L47" t="n">
         <v>7.14</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.26</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45982.55208333334</v>
+        <v>45985.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1699</v>
+        <v>1660.6</v>
       </c>
       <c r="I48" t="n">
         <v>1693.744573309886</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.15</v>
+        <v>-7.29</v>
       </c>
       <c r="L48" t="n">
         <v>8.15</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.68</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1551</v>
+        <v>1648</v>
       </c>
       <c r="I49" t="n">
         <v>1572.976815541332</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K49" t="n">
-        <v>6.6</v>
+        <v>0.76</v>
       </c>
       <c r="L49" t="n">
         <v>2.54</v>
@@ -3234,7 +3821,7 @@
         <v>0.82</v>
       </c>
       <c r="N49" t="n">
-        <v>2.67</v>
+        <v>7.83</v>
       </c>
       <c r="O49" t="n">
         <v>-1.71</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.85</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46031.38541666666</v>
+        <v>46031.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1590.9</v>
+        <v>1569.8</v>
       </c>
       <c r="I50" t="n">
         <v>1570.415847108918</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.46</v>
+        <v>-4.75</v>
       </c>
       <c r="L50" t="n">
         <v>5.89</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.06</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46049.38541666666</v>
+        <v>46049.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>1488.6</v>
+        <v>1542</v>
       </c>
       <c r="I51" t="n">
         <v>1517.311964039824</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>5.17</v>
+        <v>1.77</v>
       </c>
       <c r="L51" t="n">
         <v>1.54</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.6</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46054.55208333334</v>
+        <v>46055.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1554.6</v>
+        <v>1496</v>
       </c>
       <c r="I52" t="n">
         <v>1515.793028071611</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>0.82</v>
+        <v>-2.98</v>
       </c>
       <c r="L52" t="n">
         <v>3.86</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>15.67</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46111.55208333334</v>
+        <v>46113.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1194.9</v>
+        <v>1357</v>
       </c>
       <c r="I53" t="n">
         <v>1317.501813425893</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K53" t="n">
-        <v>20.13</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L53" t="n">
         <v>6.8</v>
@@ -3462,7 +4097,7 @@
         <v>5.05</v>
       </c>
       <c r="N53" t="n">
-        <v>4.16</v>
+        <v>12.14</v>
       </c>
       <c r="O53" t="n">
         <v>-2.25</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>15.91</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1721</v>
+        <v>1644.4</v>
       </c>
       <c r="I54" t="n">
         <v>1684.953260230439</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K54" t="n">
-        <v>26.82</v>
+        <v>21.18</v>
       </c>
       <c r="L54" t="n">
         <v>9.5</v>
@@ -3519,7 +4166,7 @@
         <v>2.99</v>
       </c>
       <c r="N54" t="n">
-        <v>2.74</v>
+        <v>5.61</v>
       </c>
       <c r="O54" t="n">
         <v>12.14</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.04</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46190.38541666666</v>
+        <v>46190.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1469</v>
+        <v>1512</v>
       </c>
       <c r="I55" t="n">
         <v>1471.464401645605</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>10.67</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L55" t="n">
         <v>4.48</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.96</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46210.38541666666</v>
+        <v>46210.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1455</v>
+        <v>1430.6</v>
       </c>
       <c r="I56" t="n">
         <v>1442.553680367738</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.77</v>
+        <v>-5.38</v>
       </c>
       <c r="L56" t="n">
         <v>6.22</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.19</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46234.38541666666</v>
+        <v>46234.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>1418.5</v>
+        <v>1430</v>
       </c>
       <c r="I57" t="n">
         <v>1428.174726306438</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K57" t="n">
-        <v>0.85</v>
+        <v>0.04</v>
       </c>
       <c r="L57" t="n">
         <v>2.45</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.05</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46265.55208333334</v>
+        <v>46266.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1507</v>
+        <v>1483.8</v>
       </c>
       <c r="I58" t="n">
         <v>1492.243623794844</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>5.38</v>
+        <v>3.76</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -3747,7 +4442,7 @@
         <v>2.69</v>
       </c>
       <c r="N58" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="O58" t="n">
         <v>2.07</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>5.5</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46272.55208333334</v>
+        <v>46273.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1509.9</v>
+        <v>1526.1</v>
       </c>
       <c r="I59" t="n">
         <v>1519.13262791972</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.76</v>
+        <v>-2.85</v>
       </c>
       <c r="L59" t="n">
-        <v>2.64</v>
+        <v>3.21</v>
       </c>
       <c r="M59" t="n">
         <v>0.67</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>4.89</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46275.55208333334</v>
+        <v>46276.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1525</v>
+        <v>1388.9</v>
       </c>
       <c r="I60" t="n">
         <v>1475.597229649068</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-8.99</v>
       </c>
       <c r="L60" t="n">
-        <v>1.57</v>
+        <v>9.57</v>
       </c>
       <c r="M60" t="n">
-        <v>0.26</v>
+        <v>0.98</v>
       </c>
       <c r="N60" t="n">
-        <v>2.06</v>
+        <v>9.44</v>
       </c>
       <c r="O60" t="n">
         <v>1.1</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3921,6 +4652,14 @@
       <c r="Q61" t="n">
         <v>60</v>
       </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6023,7 +6762,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.7</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="6">
@@ -6033,7 +6772,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -6043,7 +6782,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153.2</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
@@ -6053,7 +6792,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -6063,7 +6802,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -6073,7 +6812,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57.4</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="11">
@@ -6113,7 +6852,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.68</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="15">
@@ -6123,7 +6862,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13.83</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="16">
@@ -6133,7 +6872,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.36</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="17">
@@ -6143,7 +6882,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100.69</v>
+        <v>96.23</v>
       </c>
     </row>
     <row r="18">
@@ -6153,7 +6892,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.8</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="19">
@@ -6163,7 +6902,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.66</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="20">
@@ -6173,7 +6912,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.36</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="21">
@@ -6183,7 +6922,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.5</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="22">
@@ -6193,7 +6932,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -6203,7 +6942,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -6213,7 +6952,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="25">
@@ -6223,7 +6962,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.09</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="26">
@@ -6233,7 +6972,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.99</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="27">
@@ -6243,7 +6982,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.53</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="28">
@@ -6253,7 +6992,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
